--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0003T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76.44963013057254</v>
+        <v>12.42306489621804</v>
       </c>
       <c r="D2" t="n">
-        <v>76.63849447886602</v>
+        <v>12.45375535281573</v>
       </c>
       <c r="E2" t="n">
-        <v>31.6896637764441</v>
+        <v>5.149570363672167</v>
       </c>
       <c r="F2" t="n">
-        <v>31.78453826866383</v>
+        <v>5.164987468657873</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.376197586041881</v>
+        <v>0.7111321077318057</v>
       </c>
       <c r="D3" t="n">
-        <v>4.380332706052722</v>
+        <v>0.7118040647335674</v>
       </c>
       <c r="E3" t="n">
-        <v>31.6896637764441</v>
+        <v>5.149570363672167</v>
       </c>
       <c r="F3" t="n">
-        <v>31.78453826866383</v>
+        <v>5.164987468657873</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.45050617945795</v>
+        <v>2.510707254161916</v>
       </c>
       <c r="D4" t="n">
-        <v>15.40514162143507</v>
+        <v>2.5033355134832</v>
       </c>
       <c r="E4" t="n">
-        <v>31.6896637764441</v>
+        <v>5.149570363672167</v>
       </c>
       <c r="F4" t="n">
-        <v>31.78453826866383</v>
+        <v>5.164987468657873</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
